--- a/data/usuarios.xlsx
+++ b/data/usuarios.xlsx
@@ -2,41 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonzagay\Documents\Automatización\FrameworkYGL\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D726CDD3-4498-4E7C-B8D1-EA667B4AD022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE553C0-5253-409F-8F73-406BF4EF61EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F73C9C79-0F55-4E71-8BFA-77C6041FE751}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+  <si>
+    <t>nombre</t>
+  </si>
   <si>
     <t>usuario</t>
   </si>
@@ -44,6 +31,15 @@
     <t>correo</t>
   </si>
   <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>Martha Samano</t>
+  </si>
+  <si>
     <t>pema@gloablhitss.com</t>
   </si>
   <si>
@@ -62,37 +58,17 @@
     <t>c4rr3ra#1</t>
   </si>
   <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>perfil</t>
-  </si>
-  <si>
-    <t>Martha Perea</t>
-  </si>
-  <si>
-    <t>pema2</t>
+    <t>samano5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -115,20 +91,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -456,70 +429,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B472BB89-9F37-4987-8A2B-E9B84803F1CC}">
-  <dimension ref="A1:E3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>59</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{4062EE6C-138D-419F-9721-74A629D68DA8}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{A78DF1F5-60BF-4212-A2F4-44986AFE8FC5}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E1 A3:E4 A2 C2:E2" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>